--- a/1-Y2K-QA-ANALISIS-FUNCIONAL/DOCUMENTOS/ANALISIS_FUNCIONAL_HU_02_CAMBIAR CONTRASEÑA_Y2K.xlsx
+++ b/1-Y2K-QA-ANALISIS-FUNCIONAL/DOCUMENTOS/ANALISIS_FUNCIONAL_HU_02_CAMBIAR CONTRASEÑA_Y2K.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niury\MEGA\NIURYS\Testing\TESTING-PROYECTO-ESTUDIO-NIURYS-QA\02-PORTFOLIO\Y2K-Análisis Funcional\HU-02-reset-password\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\NIURYS-PORTAFOLIO-QA\1-Y2K-QA-ANALISIS-FUNCIONAL\DOCUMENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="HU-02 Historia de Usuario" sheetId="1" r:id="rId1"/>
@@ -1121,15 +1121,6 @@
     <t>Solicitud exitosa — mismo mensaje siempre</t>
   </si>
   <si>
-    <t>Given que el usuario 'testuser01' existe y tiene correo 'testuser01@gmail.com' registrado
-And se encuentra en el formulario de solicitud de reset
-When ingresa 'testuser01' en el campo Usuario
-And ingresa 'testuser01@gmail.com' en el campo Correo
-And hace clic en 'Aceptar'
-Then el sistema debe mostrar: 'Le enviamos un correo con instrucciones para el cambio de contraseña. Si no lo recibe, revise su carpeta de spam.'
-And debe enviar el correo con el enlace de reset al correo registrado</t>
-  </si>
-  <si>
     <t>RN-R-02, RN-R-04</t>
   </si>
   <si>
@@ -1733,9 +1724,6 @@
     <t>Correo (solicitud)</t>
   </si>
   <si>
-    <t>testuser01@gmail.com</t>
-  </si>
-  <si>
     <t>Nueva contraseña válida 1</t>
   </si>
   <si>
@@ -2202,13 +2190,25 @@
   </si>
   <si>
     <t>El sistema requiere dos datos obligatorios: nombre de usuario y correo electrónico. Ambos deben completarse.</t>
+  </si>
+  <si>
+    <t>Given que el usuario 'testuser01' existe y tiene correo 'testuser01@gmail.com' registrado
+And se encuentra en el formulario de solicitud de reset
+When ingresa 'testuser01' en el campo Usuario
+And ingresa testuser01@ejemplo.com' en el campo Correo
+And hace clic en 'Aceptar'
+Then el sistema debe mostrar: 'Le enviamos un correo con instrucciones para el cambio de contraseña. Si no lo recibe, revise su carpeta de spam.'
+And debe enviar el correo con el enlace de reset al correo registrado</t>
+  </si>
+  <si>
+    <t>testuser01@ejemplo.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2251,8 +2251,16 @@
       <name val="Arial"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2442,10 +2450,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2498,9 +2507,6 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2513,9 +2519,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2524,6 +2527,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2554,8 +2560,15 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2866,494 +2879,494 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>681</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="19" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="21"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="21"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="19" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="22"/>
+      <c r="C9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="19" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="21"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="21"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="22"/>
+      <c r="C28" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="21"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="22"/>
+      <c r="C29" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="21"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="22"/>
+      <c r="C30" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="21"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
     </row>
     <row r="31" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="22"/>
+      <c r="C31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="21"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
     </row>
     <row r="32" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="19" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="21"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="22"/>
+      <c r="C33" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="21"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="22"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="21"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="20"/>
     </row>
     <row r="35" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="19" t="s">
+      <c r="B35" s="22"/>
+      <c r="C35" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="21"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="20"/>
     </row>
     <row r="36" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="22"/>
+      <c r="C36" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="21"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="20"/>
     </row>
     <row r="37" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="22"/>
+      <c r="C37" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="21"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
     </row>
     <row r="38" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="22"/>
+      <c r="C38" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="21"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
     </row>
     <row r="39" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="22"/>
+      <c r="C39" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="21"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="20"/>
     </row>
     <row r="40" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="19" t="s">
+      <c r="B40" s="22"/>
+      <c r="C40" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="21"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="20"/>
     </row>
     <row r="41" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="19" t="s">
+      <c r="B41" s="22"/>
+      <c r="C41" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="21"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
     </row>
     <row r="42" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="19" t="s">
+      <c r="B42" s="22"/>
+      <c r="C42" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="21"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="20"/>
     </row>
     <row r="43" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="19" t="s">
+      <c r="B43" s="22"/>
+      <c r="C43" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="21"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="20"/>
     </row>
     <row r="44" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="19" t="s">
+      <c r="B44" s="22"/>
+      <c r="C44" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="21"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="20"/>
     </row>
     <row r="45" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="19" t="s">
+      <c r="B45" s="22"/>
+      <c r="C45" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="21"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="20"/>
     </row>
     <row r="46" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="19" t="s">
+      <c r="B46" s="22"/>
+      <c r="C46" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="21"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="20"/>
     </row>
     <row r="47" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="19" t="s">
+      <c r="B47" s="22"/>
+      <c r="C47" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="21"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="20"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
+      <c r="A49" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
@@ -3362,11 +3375,11 @@
       <c r="B50" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="28"/>
-      <c r="E50" s="29"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
       <c r="F50" s="2" t="s">
         <v>74</v>
       </c>
@@ -3378,11 +3391,11 @@
       <c r="B51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="20"/>
       <c r="F51" s="1" t="s">
         <v>78</v>
       </c>
@@ -3394,11 +3407,11 @@
       <c r="B52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="21"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="20"/>
       <c r="F52" s="1" t="s">
         <v>82</v>
       </c>
@@ -3410,11 +3423,11 @@
       <c r="B53" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20"/>
       <c r="F53" s="1" t="s">
         <v>78</v>
       </c>
@@ -3426,11 +3439,11 @@
       <c r="B54" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="21"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="20"/>
       <c r="F54" s="1" t="s">
         <v>78</v>
       </c>
@@ -3442,11 +3455,11 @@
       <c r="B55" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="21"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20"/>
       <c r="F55" s="1" t="s">
         <v>92</v>
       </c>
@@ -3458,11 +3471,11 @@
       <c r="B56" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="20"/>
       <c r="F56" s="1" t="s">
         <v>78</v>
       </c>
@@ -3474,11 +3487,11 @@
       <c r="B57" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="21"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="20"/>
       <c r="F57" s="1" t="s">
         <v>78</v>
       </c>
@@ -3490,17 +3503,83 @@
       <c r="B58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="21"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="20"/>
       <c r="F58" s="1" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="C51:E51"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A41:B41"/>
@@ -3517,72 +3596,6 @@
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C57:E57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3601,31 +3614,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>684</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -3832,13 +3845,13 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -4164,13 +4177,13 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
@@ -4275,13 +4288,13 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
+      <c r="A47" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
@@ -4352,13 +4365,13 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
+      <c r="A53" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
@@ -4446,13 +4459,13 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="24" t="s">
+      <c r="A60" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
@@ -4523,13 +4536,13 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
@@ -4600,13 +4613,13 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="24" t="s">
+      <c r="A72" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
@@ -4677,13 +4690,13 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="24" t="s">
+      <c r="A78" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
@@ -4738,17 +4751,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A47:E47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4767,31 +4780,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>685</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -4832,7 +4845,7 @@
         <v>233</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>234</v>
@@ -4896,13 +4909,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -5041,13 +5054,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -5169,13 +5182,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
@@ -5229,13 +5242,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -5366,31 +5379,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>686</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -5459,10 +5472,10 @@
         <v>362</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="128.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5473,13 +5486,13 @@
         <v>358</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="176.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5490,13 +5503,13 @@
         <v>358</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -5504,13 +5517,13 @@
         <v>236</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="10" t="s">
         <v>372</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>373</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>233</v>
@@ -5521,30 +5534,30 @@
         <v>293</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>339</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="128.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>378</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>240</v>
@@ -5555,16 +5568,16 @@
         <v>269</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -5572,13 +5585,13 @@
         <v>298</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>294</v>
@@ -5589,13 +5602,13 @@
         <v>303</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="10" t="s">
         <v>385</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>386</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>299</v>
@@ -5606,13 +5619,13 @@
         <v>313</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>387</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>388</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>309</v>
@@ -5620,33 +5633,33 @@
     </row>
     <row r="20" spans="1:5" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="C20" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="E20" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="10" t="s">
         <v>395</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>396</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>260</v>
@@ -5657,13 +5670,13 @@
         <v>308</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>398</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>304</v>
@@ -5674,16 +5687,16 @@
         <v>255</v>
       </c>
       <c r="B23" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="111.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5691,13 +5704,13 @@
         <v>274</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>270</v>
@@ -5708,13 +5721,13 @@
         <v>282</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>405</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>406</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>279</v>
@@ -5725,13 +5738,13 @@
         <v>249</v>
       </c>
       <c r="B26" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="10" t="s">
         <v>408</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>409</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>245</v>
@@ -5739,16 +5752,16 @@
     </row>
     <row r="27" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="10" t="s">
         <v>411</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>412</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>228</v>
@@ -5780,79 +5793,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="G5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>233</v>
@@ -5860,19 +5873,19 @@
     </row>
     <row r="7" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>111</v>
@@ -5881,67 +5894,67 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="G8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>121</v>
@@ -5950,166 +5963,166 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>472</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>256</v>
@@ -6117,18 +6130,18 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>245</v>
@@ -6136,18 +6149,18 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>275</v>
@@ -6157,16 +6170,16 @@
     </row>
     <row r="24" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>315</v>
@@ -6174,18 +6187,18 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>240</v>
@@ -6195,16 +6208,16 @@
     </row>
     <row r="26" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>251</v>
@@ -6212,18 +6225,18 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>270</v>
@@ -6231,18 +6244,18 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>279</v>
@@ -6251,128 +6264,128 @@
       <c r="G28" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>506</v>
-      </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
+      <c r="A30" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>527</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -6382,10 +6395,10 @@
     </row>
     <row r="39" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -6395,10 +6408,10 @@
     </row>
     <row r="40" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>689</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -6408,10 +6421,10 @@
     </row>
     <row r="41" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -6421,10 +6434,10 @@
     </row>
     <row r="42" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -6433,25 +6446,25 @@
       <c r="G42" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
-        <v>538</v>
-      </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
+      <c r="A44" s="29" t="s">
+        <v>536</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -6460,13 +6473,13 @@
     </row>
     <row r="46" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>543</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -6475,13 +6488,13 @@
     </row>
     <row r="47" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -6490,13 +6503,13 @@
     </row>
     <row r="48" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -6505,13 +6518,13 @@
     </row>
     <row r="49" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -6520,13 +6533,13 @@
     </row>
     <row r="50" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -6535,13 +6548,13 @@
     </row>
     <row r="51" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -6550,13 +6563,13 @@
     </row>
     <row r="52" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6592,443 +6605,443 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>557</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="A1" s="28" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>688</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>558</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="A4" s="29" t="s">
+        <v>556</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>567</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="E7" s="11" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
         <v>574</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>576</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="D11" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="E11" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="F11" s="16" t="s">
         <v>580</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>583</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="E12" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="F12" s="16" t="s">
         <v>586</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>589</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>590</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>591</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>592</v>
       </c>
-      <c r="E13" s="16" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>595</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="D17" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="E17" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="F17" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>600</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="D18" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>605</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="F19" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="E19" s="12" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
         <v>612</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>614</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
+        <v>613</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>614</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="D23" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="E23" s="13" t="s">
         <v>617</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="E23" s="13" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="35" t="s">
         <v>619</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
-        <v>621</v>
-      </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>623</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="E27" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="E27" s="14" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
         <v>626</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
-        <v>628</v>
-      </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="D31" s="17" t="s">
         <v>630</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="E31" s="17" t="s">
         <v>631</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="F31" s="17" t="s">
         <v>632</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>633</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
+        <v>633</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>635</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="D32" s="17" t="s">
         <v>636</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="E32" s="17" t="s">
         <v>637</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="F32" s="17" t="s">
         <v>638</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>639</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -7058,306 +7071,326 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>685</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>640</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>641</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>687</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="18" t="s">
         <v>642</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-    </row>
-    <row r="5" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>643</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="19" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>645</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="19" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="18" t="s">
         <v>646</v>
       </c>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
         <v>647</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="19" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="18" t="s">
         <v>648</v>
       </c>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>649</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="19" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="18" t="s">
         <v>650</v>
       </c>
-      <c r="D8" s="21"/>
-    </row>
-    <row r="9" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
         <v>651</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="19" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="18" t="s">
         <v>652</v>
       </c>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>653</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="19" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="18" t="s">
         <v>654</v>
       </c>
-      <c r="D10" s="21"/>
-    </row>
-    <row r="11" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
         <v>655</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="19" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="18" t="s">
         <v>656</v>
       </c>
-      <c r="D11" s="21"/>
-    </row>
-    <row r="12" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>657</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="19" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="18" t="s">
         <v>658</v>
       </c>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="D13" s="20"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>659</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="19" t="s">
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>660</v>
       </c>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="38" t="s">
         <v>661</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-    </row>
-    <row r="16" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>662</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="39" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="37" t="s">
         <v>663</v>
       </c>
-      <c r="D16" s="21"/>
-    </row>
-    <row r="17" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="37" t="s">
         <v>664</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="38" t="s">
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
         <v>665</v>
       </c>
-      <c r="D17" s="21"/>
-    </row>
-    <row r="18" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="38" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="37" t="s">
         <v>666</v>
       </c>
-      <c r="D18" s="21"/>
-    </row>
-    <row r="19" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="37" t="s">
         <v>667</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="38" t="s">
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="37" t="s">
         <v>668</v>
       </c>
-      <c r="D19" s="21"/>
-    </row>
-    <row r="20" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="38" t="s">
+      <c r="D21" s="20"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
         <v>669</v>
       </c>
-      <c r="D20" s="21"/>
-    </row>
-    <row r="21" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="38" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="20"/>
+    </row>
+    <row r="25" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="20"/>
+    </row>
+    <row r="26" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="20"/>
+    </row>
+    <row r="27" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
         <v>670</v>
       </c>
-      <c r="D21" s="21"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="18" t="s">
         <v>671</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-    </row>
-    <row r="24" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="21"/>
-    </row>
-    <row r="25" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="21"/>
-    </row>
-    <row r="26" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="21"/>
-    </row>
-    <row r="27" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+      <c r="D27" s="20"/>
+    </row>
+    <row r="28" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
         <v>672</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="19" t="s">
+      <c r="B28" s="20"/>
+      <c r="C28" s="18" t="s">
         <v>673</v>
       </c>
-      <c r="D27" s="21"/>
-    </row>
-    <row r="28" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
+      <c r="D28" s="20"/>
+    </row>
+    <row r="29" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
         <v>674</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="19" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="D28" s="21"/>
-    </row>
-    <row r="29" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
+      <c r="D29" s="20"/>
+    </row>
+    <row r="30" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="18" t="s">
         <v>676</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="19" t="s">
+      <c r="D30" s="20"/>
+    </row>
+    <row r="31" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
         <v>677</v>
       </c>
-      <c r="D29" s="21"/>
-    </row>
-    <row r="30" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="19" t="s">
+      <c r="B31" s="20"/>
+      <c r="C31" s="18" t="s">
         <v>678</v>
       </c>
-      <c r="D30" s="21"/>
-    </row>
-    <row r="31" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
+      <c r="D31" s="20"/>
+    </row>
+    <row r="32" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
         <v>679</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="19" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="18" t="s">
         <v>680</v>
       </c>
-      <c r="D31" s="21"/>
-    </row>
-    <row r="32" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="19" t="s">
-        <v>500</v>
-      </c>
-      <c r="D32" s="21"/>
-    </row>
-    <row r="33" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
-        <v>681</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="19" t="s">
-        <v>682</v>
-      </c>
-      <c r="D33" s="21"/>
+      <c r="D33" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:D16"/>
@@ -7372,38 +7405,18 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C7:D7"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C25:D25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
